--- a/artfynd/A 8865-2022 artfynd.xlsx
+++ b/artfynd/A 8865-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8865-2022 artfynd.xlsx
+++ b/artfynd/A 8865-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75571996</v>
+        <v>56206578</v>
       </c>
       <c r="B2" t="n">
-        <v>88962</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>86112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>901</v>
+        <v>147</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Narrtagging</t>
+          <t>Linddyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnocristella himantia</t>
+          <t>Biscogniauxia cinereolilacina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.:Fr.) R.H.Petersen</t>
+          <t>(J.H.Mill.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660683.9449031213</v>
+        <v>660681</v>
       </c>
       <c r="R2" t="n">
-        <v>6638769.667443123</v>
+        <v>6638809</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2000-10-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-10-26</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på död alm, omkr. 12 cm.</t>
+          <t>Små stroman på nedfallen gren, omkr. 60 cm, från levande lind, omkr. 243 cm. Växtplatsen upptäcktes av Pär Eriksson tidigare under år 2000. Sporer 13-15 x 4,5-5 μm, (lite smalare än vad som anges i litt.).</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,19 +764,25 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Strandskog vid sjö.</t>
+          <t>Äldre lövskog på blockig mark.</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Skogslind</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark på död alm. # Skogsalm</t>
-        </is>
-      </c>
+          <t>Nedfallen gren från levande lind. # Skogslind</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -804,6 +795,582 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>69546306</v>
+      </c>
+      <c r="B3" t="n">
+        <v>89141</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>821</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gulprickig vaxskivling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hygrophorus chrysodon</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Batsch) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hallkved 1 km NO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>660652</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6638780</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2001-09-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2001-09-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ca. 30 ex. under lind.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre lövskog.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>75571996</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91453</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>901</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Narrtagging</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnocristella himantia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.:Fr.) R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hallkved 1 km NO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>660684</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6638770</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2000-10-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2000-10-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På bark på död alm, omkr. 12 cm.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Strandskog vid sjö.</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark på död alm. # Skogsalm</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>59425079</v>
+      </c>
+      <c r="B5" t="n">
+        <v>88964</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3279</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Maskfingersvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Clavaria fragilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Holmsk., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hallkved 1 km NO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>660647</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6638775</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex. i skogsbryn.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>59720990</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83320</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4194</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Plattad jordtunga</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Geoglossum cookeanum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Minter &amp; P.F.Cannon</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hallkved 1 km NO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>660643</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6638774</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca. 40 ex. vid en stig i skogsbryn. Fruktkroppar smalt tungformade, något tillplattade, upp till 5 cm höga, och 1 cm tjocka, svarta med avsmalnande fot. Sporer 65-75 x 6 μm, alla 7-septerade, grönbruna. Parafyser tätt septerade, ofta insnörda vid varje septum, åtminstone i övre delen. Översta cellen i parafyserna uppsvälld, kägel-, päron- eller ballongformad, upp till 8 μm bred.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lövskogsbryn.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>59720991</v>
+      </c>
+      <c r="B7" t="n">
+        <v>89080</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4373</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sprödvaxing</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hygrocybe ceracea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Wulfen) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hallkved 1 km NO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>660647</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6638775</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca. 10 ex. i skogsbryn.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lövskogsbryn.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
